--- a/excels/demo_gears_3d (3) - BIG.xlsx
+++ b/excels/demo_gears_3d (3) - BIG.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -840,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -854,20 +854,20 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Spur pinion Z=18 m=3 FW=50mm (Al-6061)</t>
+          <t>Spur pinion Z=18 m=3 FW=50mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M4" s="5">
-        <f>ROUND(PI()*((E4*F4/2+F4)^2-(H4/2)^2)*G4*0.00000270,3)</f>
+        <f>ROUND(PI()*((E4*F4/2+F4)^2-(H4/2)^2)*G4*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>ROUND(M4*265.0,2)</f>
+        <f>ROUND(M4*125.0,2)</f>
         <v/>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>Ground hobbed; AGMA Q10; keyway 6×3.5. Material changed from Steel-4140 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>Ground hobbed; AGMA Q10; keyway 6×3.5. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -903,7 +903,7 @@
         <v>40</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -917,20 +917,20 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Spur wheel Z=54 m=4 FW=50mm (Al-6061)</t>
+          <t>Spur wheel Z=54 m=4 FW=50mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M5" s="5">
-        <f>ROUND(PI()*((E5*F5/2+F5)^2-(H5/2)^2)*G5*0.00000270,3)</f>
+        <f>ROUND(PI()*((E5*F5/2+F5)^2-(H5/2)^2)*G5*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N5" s="6">
-        <f>ROUND(M5*265.0,2)</f>
+        <f>ROUND(M5*125.0,2)</f>
         <v/>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>Hobbed; bore H7; check tip clearance. Material changed from Steel-1020 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>Hobbed; bore H7; check tip clearance. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -966,7 +966,7 @@
         <v>18</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -980,20 +980,20 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Idler gear Z=24 m=2 FW=40mm (Al-6061)</t>
+          <t>Idler gear Z=24 m=2 FW=40mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M6" s="5">
-        <f>ROUND(PI()*((E6*F6/2+F6)^2-(H6/2)^2)*G6*0.00000270,3)</f>
+        <f>ROUND(PI()*((E6*F6/2+F6)^2-(H6/2)^2)*G6*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N6" s="6">
-        <f>ROUND(M6*265.0,2)</f>
+        <f>ROUND(M6*125.0,2)</f>
         <v/>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>Anodised; PTFE-coated bore</t>
+          <t>Anodised; PTFE-coated bore. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -1029,7 +1029,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1043,20 +1043,20 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Stage-2 spur Z=36 m=4 FW=60mm (Al-6061)</t>
+          <t>Stage-2 spur Z=36 m=4 FW=60mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M7" s="5">
-        <f>ROUND(PI()*((E7*F7/2+F7)^2-(H7/2)^2)*G7*0.00000270,3)</f>
+        <f>ROUND(PI()*((E7*F7/2+F7)^2-(H7/2)^2)*G7*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N7" s="6">
-        <f>ROUND(M7*265.0,2)</f>
+        <f>ROUND(M7*125.0,2)</f>
         <v/>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>Profile shift x=+0.2; no undercut. Material changed from Steel-4140 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>Profile shift x=+0.2; no undercut. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -1092,7 +1092,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1106,20 +1106,20 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Small spur Z=12 m=1.5 FW=35mm (Al-6061)</t>
+          <t>Small spur Z=12 m=1.5 FW=35mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M8" s="5">
-        <f>ROUND(PI()*((E8*F8/2+F8)^2-(H8/2)^2)*G8*0.00000270,3)</f>
+        <f>ROUND(PI()*((E8*F8/2+F8)^2-(H8/2)^2)*G8*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N8" s="6">
-        <f>ROUND(M8*265.0,2)</f>
+        <f>ROUND(M8*125.0,2)</f>
         <v/>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>WARN Z&lt;17: profile shift required. Material changed from Steel-1020 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>WARN Z&lt;17: profile shift required. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
@@ -1358,20 +1358,20 @@
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>Helical aluminium Z=24 m=2</t>
+          <t>Helical Steel-1020 Z=24 m=2</t>
         </is>
       </c>
       <c r="M12" s="11">
-        <f>ROUND(PI()*((E12*F12/2+F12)^2-(H12/2)^2)*G12*0.00000270,3)</f>
+        <f>ROUND(PI()*((E12*F12/2+F12)^2-(H12/2)^2)*G12*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N12" s="12">
-        <f>ROUND(M12*265.0,2)</f>
+        <f>ROUND(M12*125.0,2)</f>
         <v/>
       </c>
       <c r="O12" s="13" t="inlineStr">
         <is>
-          <t>Oil mist lube; lightweight stage</t>
+          <t>Oil mist lube; lightweight stage. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -2037,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2051,20 +2051,20 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>WARN: Z=8 undercut — profile shift req; bore_d=5mm; FW=30mm (Al-6061)</t>
+          <t>WARN: Z=8 undercut — profile shift req; bore_d=5mm; FW=30mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M23" s="5">
-        <f>ROUND(PI()*((E23*F23/2+F23)^2-(H23/2)^2)*G23*0.00000270,3)</f>
+        <f>ROUND(PI()*((E23*F23/2+F23)^2-(H23/2)^2)*G23*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N23" s="6">
-        <f>ROUND(M23*265.0,2)</f>
+        <f>ROUND(M23*125.0,2)</f>
         <v/>
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>Validator should flag undercut (Z&lt;17). Material changed from Steel-1020 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>Validator should flag undercut (Z&lt;17). Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="D24" s="38" t="inlineStr">
         <is>
-          <t>Al-6061</t>
+          <t>Steel-1020</t>
         </is>
       </c>
       <c r="E24" s="38" t="n">
@@ -2100,7 +2100,7 @@
         <v>16</v>
       </c>
       <c r="I24" s="38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J24" s="38" t="inlineStr">
         <is>
@@ -2114,20 +2114,20 @@
       </c>
       <c r="L24" s="40" t="inlineStr">
         <is>
-          <t>SKIP TEST: Enabled=NO — not generated; FW=45mm (Al-6061)</t>
+          <t>SKIP TEST: Enabled=NO — not generated; FW=45mm (Steel-1020)</t>
         </is>
       </c>
       <c r="M24" s="41">
-        <f>ROUND(PI()*((E24*F24/2+F24)^2-(H24/2)^2)*G24*0.00000270,3)</f>
+        <f>ROUND(PI()*((E24*F24/2+F24)^2-(H24/2)^2)*G24*0.00000787,3)</f>
         <v/>
       </c>
       <c r="N24" s="42">
-        <f>ROUND(M24*265.0,2)</f>
+        <f>ROUND(M24*125.0,2)</f>
         <v/>
       </c>
       <c r="O24" s="40" t="inlineStr">
         <is>
-          <t>Verify engine skips this row. Material changed from Steel-1020 to Al-6061: reduced weight, lower strength, potentially lower cost.</t>
+          <t>Verify engine skips this row. Material changed from Al-6061 to Steel-1020: increased weight, higher strength, potentially higher cost.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="62" min="1" max="1"/>
@@ -3256,6 +3256,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-14 07:13:56</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AI Copilot via GUI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>change the matertials of all from aluminium to steel and change the quantity of the all spur gear from 2 to 10</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
